--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260612.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>26,879,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>26,879,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,540,000</t>
+          <t>40,840,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>40,840,000</t>
+          <t>15,540,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
